--- a/data/trans_dic/P44A$sangre-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 29,15</t>
+          <t>6,82; 30,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 17,89</t>
+          <t>3,42; 18,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,76; 70,1</t>
+          <t>56,71; 70,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 18,59</t>
+          <t>4,46; 20,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 22,88</t>
+          <t>5,3; 23,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,87; 72,93</t>
+          <t>63,3; 73,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 19,17</t>
+          <t>7,3; 19,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 17,77</t>
+          <t>5,69; 17,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,99; 70,26</t>
+          <t>61,81; 70,17</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 34,85</t>
+          <t>8,33; 33,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 18,77</t>
+          <t>3,85; 18,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,41; 94,83</t>
+          <t>66,08; 95,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,69</t>
+          <t>0,0; 21,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,35</t>
+          <t>0,0; 14,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,69; 75,8</t>
+          <t>67,42; 75,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 24,08</t>
+          <t>7,58; 24,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 14,28</t>
+          <t>3,14; 13,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,55; 91,61</t>
+          <t>68,79; 91,92</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 52,99</t>
+          <t>6,04; 52,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 37,81</t>
+          <t>6,71; 37,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,51; 67,73</t>
+          <t>51,82; 67,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,38</t>
+          <t>0,0; 34,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,0</t>
+          <t>0,0; 31,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,5; 79,41</t>
+          <t>66,22; 79,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 34,66</t>
+          <t>3,79; 34,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 25,82</t>
+          <t>6,01; 26,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,8; 70,96</t>
+          <t>59,85; 71,21</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 28,27</t>
+          <t>11,18; 27,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 16,64</t>
+          <t>6,28; 16,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,56; 89,68</t>
+          <t>63,8; 89,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 15,67</t>
+          <t>3,9; 15,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 15,51</t>
+          <t>4,34; 14,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,69; 73,86</t>
+          <t>67,7; 73,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 18,79</t>
+          <t>9,09; 19,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,08</t>
+          <t>6,47; 13,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,88; 86,8</t>
+          <t>67,0; 86,84</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3058; 13136</t>
+          <t>3074; 13522</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1744; 9254</t>
+          <t>1770; 9344</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79717; 98464</t>
+          <t>79658; 98723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2185; 11697</t>
+          <t>2803; 12597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3113; 14210</t>
+          <t>3295; 14339</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>106830; 123933</t>
+          <t>107554; 124709</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7249; 20698</t>
+          <t>7880; 21193</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6668; 20226</t>
+          <t>6472; 19840</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>192414; 218077</t>
+          <t>191855; 217802</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4174; 17338</t>
+          <t>4143; 16429</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2990; 14659</t>
+          <t>3008; 14680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>339094; 484205</t>
+          <t>337393; 486645</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5995</t>
+          <t>0; 6510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5229</t>
+          <t>0; 5239</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>148722; 169036</t>
+          <t>150358; 169173</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5265; 19310</t>
+          <t>6075; 19572</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3090; 16358</t>
+          <t>3601; 15328</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>502878; 672095</t>
+          <t>504675; 674347</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>831; 7718</t>
+          <t>880; 7666</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1886; 10943</t>
+          <t>1943; 10875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63742; 83807</t>
+          <t>64124; 83815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 4288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5489</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55785; 67638</t>
+          <t>56406; 67989</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1027; 9377</t>
+          <t>1024; 9265</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2440; 11641</t>
+          <t>2709; 12058</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>124931; 148245</t>
+          <t>125030; 148772</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12122; 30912</t>
+          <t>12226; 29752</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10104; 26414</t>
+          <t>9967; 26801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>492476; 694884</t>
+          <t>494371; 695326</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4345; 16588</t>
+          <t>4124; 16239</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4916; 17786</t>
+          <t>4977; 16132</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>323638; 353144</t>
+          <t>323663; 351987</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19516; 40442</t>
+          <t>19563; 41357</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18172; 38491</t>
+          <t>17704; 38096</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>837950; 1087480</t>
+          <t>839521; 1088090</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$sangre-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 30,01</t>
+          <t>6,7; 29,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 18,07</t>
+          <t>3,36; 17,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,71; 70,29</t>
+          <t>56,9; 70,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 20,02</t>
+          <t>4,69; 20,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 23,08</t>
+          <t>5,15; 23,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,3; 73,39</t>
+          <t>62,96; 72,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 19,63</t>
+          <t>6,73; 19,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 17,43</t>
+          <t>6,18; 18,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,81; 70,17</t>
+          <t>62,15; 70,06</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 33,02</t>
+          <t>8,22; 33,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 18,8</t>
+          <t>3,95; 18,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,08; 95,31</t>
+          <t>61,82; 72,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,39</t>
+          <t>0,0; 23,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,38</t>
+          <t>0,0; 14,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,42; 75,86</t>
+          <t>66,89; 75,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 24,41</t>
+          <t>7,88; 25,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,38</t>
+          <t>3,52; 15,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,79; 91,92</t>
+          <t>65,16; 72,27</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 52,64</t>
+          <t>6,4; 53,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 37,57</t>
+          <t>6,48; 35,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,82; 67,73</t>
+          <t>50,77; 66,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,34</t>
+          <t>0,0; 34,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 34,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,22; 79,82</t>
+          <t>66,24; 79,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 34,25</t>
+          <t>3,58; 32,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 26,74</t>
+          <t>6,05; 24,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,85; 71,21</t>
+          <t>60,04; 71,0</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 27,2</t>
+          <t>11,44; 28,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 16,88</t>
+          <t>6,5; 16,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,8; 89,74</t>
+          <t>60,76; 68,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 15,34</t>
+          <t>4,02; 15,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,06</t>
+          <t>4,45; 15,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,7; 73,62</t>
+          <t>67,39; 73,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 19,22</t>
+          <t>9,31; 19,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 13,93</t>
+          <t>6,42; 13,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,0; 86,84</t>
+          <t>65,11; 69,86</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89333</t>
+          <t>95144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>115858</t>
+          <t>127217</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>205191</t>
+          <t>222360</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3074; 13522</t>
+          <t>3018; 13156</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1770; 9344</t>
+          <t>1738; 9134</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79658; 98723</t>
+          <t>85065; 104877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2803; 12597</t>
+          <t>2950; 12699</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3295; 14339</t>
+          <t>3201; 14433</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>107554; 124709</t>
+          <t>117632; 136118</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7880; 21193</t>
+          <t>7268; 21138</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6472; 19840</t>
+          <t>7032; 21082</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>191855; 217802</t>
+          <t>209048; 235651</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425270</t>
+          <t>194244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>159813</t>
+          <t>174602</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>585083</t>
+          <t>368845</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4143; 16429</t>
+          <t>4089; 16811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3008; 14680</t>
+          <t>3087; 14701</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>337393; 486645</t>
+          <t>179140; 208775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6510</t>
+          <t>0; 7283</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5239</t>
+          <t>0; 5430</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>150358; 169173</t>
+          <t>163745; 185699</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6075; 19572</t>
+          <t>6321; 20500</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3601; 15328</t>
+          <t>4029; 18166</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>504675; 674347</t>
+          <t>348359; 386363</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>76854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>71085</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>136777</t>
+          <t>147939</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>880; 7666</t>
+          <t>932; 7726</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1943; 10875</t>
+          <t>1875; 10281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64124; 83815</t>
+          <t>65755; 86562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4288</t>
+          <t>0; 4352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5116</t>
+          <t>0; 5625</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56406; 67989</t>
+          <t>63996; 77189</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1024; 9265</t>
+          <t>968; 8755</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2709; 12058</t>
+          <t>2728; 11209</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125030; 148772</t>
+          <t>135767; 160560</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739145</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12226; 29752</t>
+          <t>12508; 30662</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9967; 26801</t>
+          <t>10323; 26755</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>494371; 695326</t>
+          <t>345589; 387707</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4124; 16239</t>
+          <t>4253; 16285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4977; 16132</t>
+          <t>5099; 17336</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>323663; 351987</t>
+          <t>356019; 388187</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19563; 41357</t>
+          <t>20032; 40898</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17704; 38096</t>
+          <t>17549; 37839</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>839521; 1088090</t>
+          <t>714309; 766440</t>
         </is>
       </c>
     </row>
